--- a/DateBase/orders/Dang Nguyen48_2026-6-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-10.xlsx
@@ -524,6 +524,9 @@
       <c r="C11" t="str">
         <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -582,7 +585,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010105510203080</v>
+        <v>010101055102030816</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -528,9 +528,92 @@
         <v>16</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>4</v>
+      </c>
+      <c r="C14" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>317_尤加利叶细叶_Eucalyptus Parvifolia_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>5</v>
+      </c>
+      <c r="C20" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>558_油画小菊_Helenium_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -585,7 +668,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010101055102030816</v>
+        <v>01010105510203081691514599610150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-10.xlsx
@@ -610,6 +610,9 @@
       <c r="C21" t="str">
         <v>558_油画小菊_Helenium_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -668,7 +671,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010105510203081691514599610150</v>
+        <v>01010105510203081691514599610152</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -611,12 +611,95 @@
         <v>558_油画小菊_Helenium_undefined_1bunch</v>
       </c>
       <c r="F21" t="str">
-        <v>2</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F22" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>102_绣球重瓣白_Hydrangea White D_Hydrangea L._1stem</v>
+      </c>
+      <c r="F23" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>6</v>
+      </c>
+      <c r="C27" t="str">
+        <v>614_康乃馨绿_green_undefined_20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v>606_康乃馨橙光_orange_undefined_20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>782_松果菊绿_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>783_松果菊粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -671,7 +754,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010105510203081691514599610152</v>
+        <v>010101055102030816915145996101520203030101055550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-10.xlsx
@@ -696,6 +696,9 @@
       <c r="C31" t="str">
         <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -754,7 +757,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010101055102030816915145996101520203030101055550</v>
+        <v>010101055102030816915145996101520203030101055555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -700,9 +700,20 @@
         <v>5</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>7</v>
+      </c>
+      <c r="C32" t="str">
+        <v>761_芍药奶油碗_undefined_undefined_10stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -757,7 +768,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010101055102030816915145996101520203030101055555</v>
+        <v>010101055102030816915145996101520203030101055555100</v>
       </c>
     </row>
   </sheetData>
